--- a/data/pkaanion.xlsx
+++ b/data/pkaanion.xlsx
@@ -590,6 +590,7 @@
   <dimension ref="A1:B81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="55.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
